--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12337,7 +12337,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>Field Coordination</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P165"/>
+  <dimension ref="A1:P166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12341,8 +12341,80 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-3108</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Biocontainment Network Investigation</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Control Network</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>VMware</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Biosecurity Segment</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>National Response Cell</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P165"/>
+  <autoFilter ref="A1:P166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12409,7 +12409,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12413,8 +12413,80 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-8600</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Protected Research Systems Investigation</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Control Network</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Containment Network</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>National Response Cell</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P166"/>
+  <autoFilter ref="A1:P167"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12481,7 +12481,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P167"/>
+  <dimension ref="A1:P168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12485,8 +12485,80 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-5449</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Protected Research Systems Investigation</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>331</v>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Research Environment</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>VMware</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Containment Network</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Team Delta</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>Field Coordination</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P167"/>
+  <autoFilter ref="A1:P168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12553,7 +12553,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>Field Coordination</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P168"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12557,8 +12557,80 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-7479</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Protected Research Systems Investigation</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>ROUTINE</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>Medical Research Laboratory</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Secure Laboratory</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Team Delta</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>Intelligence Analysis</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P168"/>
+  <autoFilter ref="A1:P169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12625,7 +12625,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>Intelligence Analysis</t>
+          <t>RESOLVED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P169"/>
+  <dimension ref="A1:P170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12629,8 +12629,80 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-1222</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Specimen Management Security Review</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>ROUTINE</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>Evidence Processing Network</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>Red Hat</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Evidence Network</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Team Delta</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>Evidence Collection</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P169"/>
+  <autoFilter ref="A1:P170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12697,7 +12697,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>Evidence Collection</t>
+          <t>RESOLVED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P170"/>
+  <dimension ref="A1:P171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12701,8 +12701,80 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-2862</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Security Investigation</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Research Environment</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Evidence Network</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Team Delta</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P170"/>
+  <autoFilter ref="A1:P171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P171"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12773,8 +12773,80 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-8942</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Research Facility Intrusion Investigation</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>Protected Research Network</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>VMware</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Biosecurity Segment</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>BioDefense Task Force</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>Containment</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P171"/>
+  <autoFilter ref="A1:P172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12841,7 +12841,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>Containment</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P172"/>
+  <dimension ref="A1:P173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12845,8 +12845,80 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-8272</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Research Facility Intrusion Investigation</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>Biosecurity Operations Center</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Biosecurity Segment</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Team Bravo</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>Evidence Collection</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P172"/>
+  <autoFilter ref="A1:P173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12913,7 +12913,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>Evidence Collection</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P173"/>
+  <dimension ref="A1:P174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12917,8 +12917,80 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-6011</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Biocontainment Network Investigation</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>ELEVATED</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory Control Network</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Secure Laboratory</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Team Alpha</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>Intelligence Analysis</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P173"/>
+  <autoFilter ref="A1:P174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -12985,7 +12985,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>Intelligence Analysis</t>
+          <t>RESOLVED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P174"/>
+  <dimension ref="A1:P175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12989,8 +12989,80 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-8012</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Biological Research Intelligence Collection</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>Research Data Repository</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Biosecurity Segment</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Analyst Team Bravo</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P174"/>
+  <autoFilter ref="A1:P175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -13057,7 +13057,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>ESCALATED</t>
         </is>
       </c>
     </row>

--- a/workbooks/Exposure-Tracking-Matrix.xlsx
+++ b/workbooks/Exposure-Tracking-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Investigations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Investigations'!$A$1:$P$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P175"/>
+  <dimension ref="A1:P176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13061,8 +13061,80 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>BID-2026-4555</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Coordinated Biomedical Systems Intrusion</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Protected Research Systems Investigation</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>Research Data Repository</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Protected Research Segment</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>National Response Cell</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>Intelligence Analysis</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P175"/>
+  <autoFilter ref="A1:P176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>